--- a/src/index spreadsheet/GTK key codes.xlsx
+++ b/src/index spreadsheet/GTK key codes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/wp43s archive/2024-09-01 WIP/wp43s/src/index spreadsheet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/wp43s/src/index spreadsheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB355B3-1F98-114D-9252-A0E25E8E639B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F1B2C8-6BE6-2E46-B954-FE94A0CE4B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4660" yWindow="3400" windowWidth="28040" windowHeight="17440" xr2:uid="{E19FABB6-FEBD-1F48-A261-18932C58251D}"/>
   </bookViews>
@@ -39,6 +39,28 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6196" uniqueCount="5078">
   <si>
@@ -15280,7 +15302,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -15292,6 +15314,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Consolas"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Menlo"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -15363,7 +15391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -15381,6 +15409,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15706,15 +15735,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55634599-576E-F14E-B4F1-424FAC338D75}">
-  <dimension ref="A1:F2278"/>
+  <dimension ref="A1:H2278"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
     <col min="2" max="2" width="36.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1">
         <f t="shared" ref="A1:A64" si="0">HEX2DEC(MID(C1,3,99))</f>
         <v>32</v>
@@ -15737,7 +15767,7 @@
         <v>FF08</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -15760,7 +15790,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -15783,7 +15813,7 @@
         <v>FF51</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -15799,7 +15829,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -15814,8 +15844,23 @@
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E5">
+        <v>65505</v>
+      </c>
+      <c r="F5" t="str">
+        <f>DEC2HEX(E5)</f>
+        <v>FFE1</v>
+      </c>
+      <c r="G5">
+        <f>MATCH(E5,D:D,0)</f>
+        <v>1358</v>
+      </c>
+      <c r="H5" t="str" cm="1">
+        <f t="array" ref="H5">INDEX(B:B,G5)</f>
+        <v>GDK_KEY_Shift_L</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -15830,8 +15875,23 @@
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E6" s="13">
+        <v>65507</v>
+      </c>
+      <c r="F6" t="str">
+        <f>DEC2HEX(E6)</f>
+        <v>FFE3</v>
+      </c>
+      <c r="G6">
+        <f>MATCH(E6,D:D,0)</f>
+        <v>1360</v>
+      </c>
+      <c r="H6" t="str" cm="1">
+        <f t="array" ref="H6">INDEX(B:B,G6)</f>
+        <v>GDK_KEY_Control_L</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -15846,8 +15906,23 @@
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E7" s="13">
+        <v>65514</v>
+      </c>
+      <c r="F7" t="str">
+        <f>DEC2HEX(E7)</f>
+        <v>FFEA</v>
+      </c>
+      <c r="G7">
+        <f>MATCH(E7,D:D,0)</f>
+        <v>1367</v>
+      </c>
+      <c r="H7" t="str" cm="1">
+        <f t="array" ref="H7">INDEX(B:B,G7)</f>
+        <v>GDK_KEY_Alt_R</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -15862,8 +15937,23 @@
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E8">
+        <v>92</v>
+      </c>
+      <c r="F8" t="str">
+        <f>DEC2HEX(E8)</f>
+        <v>5C</v>
+      </c>
+      <c r="G8">
+        <f>MATCH(E8,D:D,0)</f>
+        <v>62</v>
+      </c>
+      <c r="H8" t="str" cm="1">
+        <f t="array" ref="H8">INDEX(B:B,G8)</f>
+        <v>GDK_KEY_backslash</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -15878,8 +15968,23 @@
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E9" s="13">
+        <v>65364</v>
+      </c>
+      <c r="F9" t="str">
+        <f>DEC2HEX(E9)</f>
+        <v>FF54</v>
+      </c>
+      <c r="G9">
+        <f>MATCH(E9,D:D,0)</f>
+        <v>1234</v>
+      </c>
+      <c r="H9" t="str" cm="1">
+        <f t="array" ref="H9">INDEX(B:B,G9)</f>
+        <v>GDK_KEY_Down</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -15895,7 +16000,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -15911,7 +16016,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -15927,7 +16032,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -15943,7 +16048,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -15959,7 +16064,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -15975,7 +16080,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>46</v>

--- a/src/index spreadsheet/GTK key codes.xlsx
+++ b/src/index spreadsheet/GTK key codes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/wp43s/src/index spreadsheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F1B2C8-6BE6-2E46-B954-FE94A0CE4B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E8ED3B-C15D-DC4C-A7A1-AB95631BAD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4660" yWindow="3400" windowWidth="28040" windowHeight="17440" xr2:uid="{E19FABB6-FEBD-1F48-A261-18932C58251D}"/>
   </bookViews>
@@ -15828,6 +15828,21 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
+      <c r="E4">
+        <v>65505</v>
+      </c>
+      <c r="F4" t="str">
+        <f>DEC2HEX(E4)</f>
+        <v>FFE1</v>
+      </c>
+      <c r="G4">
+        <f>MATCH(E4,D:D,0)</f>
+        <v>1358</v>
+      </c>
+      <c r="H4" t="str" cm="1">
+        <f t="array" ref="H4">INDEX(B:B,G4)</f>
+        <v>GDK_KEY_Shift_L</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
@@ -15845,19 +15860,19 @@
         <v>36</v>
       </c>
       <c r="E5">
-        <v>65505</v>
+        <v>65506</v>
       </c>
       <c r="F5" t="str">
         <f>DEC2HEX(E5)</f>
-        <v>FFE1</v>
+        <v>FFE2</v>
       </c>
       <c r="G5">
         <f>MATCH(E5,D:D,0)</f>
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H5" t="str" cm="1">
         <f t="array" ref="H5">INDEX(B:B,G5)</f>
-        <v>GDK_KEY_Shift_L</v>
+        <v>GDK_KEY_Shift_R</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -15998,6 +16013,21 @@
       <c r="D10">
         <f t="shared" si="1"/>
         <v>40</v>
+      </c>
+      <c r="E10">
+        <v>65513</v>
+      </c>
+      <c r="F10" t="str">
+        <f>DEC2HEX(E10)</f>
+        <v>FFE9</v>
+      </c>
+      <c r="G10">
+        <f>MATCH(E10,D:D,0)</f>
+        <v>1366</v>
+      </c>
+      <c r="H10" t="str" cm="1">
+        <f t="array" ref="H10">INDEX(B:B,G10)</f>
+        <v>GDK_KEY_Alt_L</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
